--- a/Result/profitability/4707.xlsx
+++ b/Result/profitability/4707.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AM74"/>
+  <dimension ref="A1:AM75"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -669,10 +669,10 @@
         <v>0.34</v>
       </c>
       <c r="M2" t="n">
-        <v>0.2475</v>
+        <v>0.275</v>
       </c>
       <c r="N2" t="n">
-        <v>4.213749999999999</v>
+        <v>5.5825</v>
       </c>
       <c r="O2" t="n">
         <v>1</v>
@@ -681,7 +681,7 @@
         <v>1</v>
       </c>
       <c r="Q2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R2" t="n">
         <v>1</v>
@@ -690,7 +690,7 @@
         <v>1</v>
       </c>
       <c r="T2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="U2" t="n">
         <v>1</v>
@@ -780,10 +780,10 @@
         <v>0.5</v>
       </c>
       <c r="M3" t="n">
-        <v>0.28375</v>
+        <v>0.30375</v>
       </c>
       <c r="N3" t="n">
-        <v>9.279999999999999</v>
+        <v>10.0325</v>
       </c>
       <c r="O3" t="n">
         <v>1</v>
@@ -899,13 +899,13 @@
         <v>0.28</v>
       </c>
       <c r="M4" t="n">
-        <v>0.285</v>
+        <v>0.31125</v>
       </c>
       <c r="N4" t="n">
-        <v>15.10625</v>
+        <v>16.97</v>
       </c>
       <c r="O4" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="P4" t="n">
         <v>1</v>
@@ -917,7 +917,7 @@
         <v>1</v>
       </c>
       <c r="S4" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="T4" t="n">
         <v>0</v>
@@ -1018,10 +1018,10 @@
         <v>0.78</v>
       </c>
       <c r="M5" t="n">
-        <v>0.355</v>
+        <v>0.39875</v>
       </c>
       <c r="N5" t="n">
-        <v>19.8475</v>
+        <v>21.86625</v>
       </c>
       <c r="O5" t="n">
         <v>1</v>
@@ -1137,10 +1137,10 @@
         <v>0.03</v>
       </c>
       <c r="M6" t="n">
-        <v>0.34875</v>
+        <v>0.36375</v>
       </c>
       <c r="N6" t="n">
-        <v>24.52</v>
+        <v>25.89625</v>
       </c>
       <c r="O6" t="n">
         <v>0</v>
@@ -1264,10 +1264,10 @@
         <v>-0.15</v>
       </c>
       <c r="M7" t="n">
-        <v>0.29125</v>
+        <v>0.30875</v>
       </c>
       <c r="N7" t="n">
-        <v>29.57625</v>
+        <v>31.06375</v>
       </c>
       <c r="O7" t="n">
         <v>0</v>
@@ -1391,10 +1391,10 @@
         <v>0.1</v>
       </c>
       <c r="M8" t="n">
-        <v>0.2675</v>
+        <v>0.2887500000000001</v>
       </c>
       <c r="N8" t="n">
-        <v>34.5575</v>
+        <v>36.4925</v>
       </c>
       <c r="O8" t="n">
         <v>0</v>
@@ -9830,6 +9830,133 @@
       </c>
       <c r="AM74" t="n">
         <v>115.1</v>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="inlineStr">
+        <is>
+          <t>4707</t>
+        </is>
+      </c>
+      <c r="B75" t="inlineStr">
+        <is>
+          <t>115.2Q</t>
+        </is>
+      </c>
+      <c r="C75" t="n">
+        <v>313</v>
+      </c>
+      <c r="D75" t="n">
+        <v>277</v>
+      </c>
+      <c r="E75" t="n">
+        <v>36</v>
+      </c>
+      <c r="F75" t="n">
+        <v>11.45</v>
+      </c>
+      <c r="G75" t="n">
+        <v>8</v>
+      </c>
+      <c r="H75" t="inlineStr">
+        <is>
+          <t>2.44%</t>
+        </is>
+      </c>
+      <c r="I75" t="n">
+        <v>168</v>
+      </c>
+      <c r="J75" t="n">
+        <v>176</v>
+      </c>
+      <c r="K75" t="n">
+        <v>175</v>
+      </c>
+      <c r="L75" t="n">
+        <v>0.43</v>
+      </c>
+      <c r="M75" t="n">
+        <v>0.25875</v>
+      </c>
+      <c r="N75" t="n">
+        <v>0.6474999999999996</v>
+      </c>
+      <c r="O75" t="n">
+        <v>1</v>
+      </c>
+      <c r="P75" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q75" t="n">
+        <v>1</v>
+      </c>
+      <c r="R75" t="n">
+        <v>1</v>
+      </c>
+      <c r="S75" t="n">
+        <v>1</v>
+      </c>
+      <c r="T75" t="n">
+        <v>1</v>
+      </c>
+      <c r="U75" t="n">
+        <v>1</v>
+      </c>
+      <c r="V75" t="n">
+        <v>115.2</v>
+      </c>
+      <c r="W75" t="n">
+        <v>0.17</v>
+      </c>
+      <c r="X75" t="n">
+        <v>0.6538461538461537</v>
+      </c>
+      <c r="Y75" t="n">
+        <v>15.48</v>
+      </c>
+      <c r="Z75" t="n">
+        <v>-3.841191066997518</v>
+      </c>
+      <c r="AA75" t="n">
+        <v>0.35</v>
+      </c>
+      <c r="AB75" t="n">
+        <v>4.375</v>
+      </c>
+      <c r="AC75" t="n">
+        <v>16.15</v>
+      </c>
+      <c r="AD75" t="n">
+        <v>-3.436170212765957</v>
+      </c>
+      <c r="AE75" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF75" t="n">
+        <v>1</v>
+      </c>
+      <c r="AG75" t="n">
+        <v>1</v>
+      </c>
+      <c r="AH75" t="n">
+        <v>1</v>
+      </c>
+      <c r="AI75" t="n">
+        <v>1</v>
+      </c>
+      <c r="AJ75" t="inlineStr">
+        <is>
+          <t>EPS成長 / 毛利率成長</t>
+        </is>
+      </c>
+      <c r="AK75" t="n">
+        <v>115</v>
+      </c>
+      <c r="AL75" t="n">
+        <v>2</v>
+      </c>
+      <c r="AM75" t="n">
+        <v>115.2</v>
       </c>
     </row>
   </sheetData>
